--- a/config/yunying/loginweal.xlsx
+++ b/config/yunying/loginweal.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1日ログイン報酬</t>
+          <t>每日登录奖励</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>2日ログイン報酬</t>
+          <t>2天登录奖励</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>3日ログイン報酬</t>
+          <t>3天登录奖励</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>4日ログイン報酬</t>
+          <t>4天登录奖励</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>5日ログイン報酬</t>
+          <t>5天登录奖励</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>6日ログイン報酬</t>
+          <t>6天登录奖励</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>7日ログイン報酬</t>
+          <t>7天登录奖励</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>1日ログイン報酬</t>
+          <t>每日登录奖励</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2日ログイン報酬</t>
+          <t>2天登录奖励</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3日ログイン報酬</t>
+          <t>3天登录奖励</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>4日ログイン報酬</t>
+          <t>4天登录奖励</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5日ログイン報酬</t>
+          <t>5天登录奖励</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6日ログイン報酬</t>
+          <t>6天登录奖励</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7日ログイン報酬</t>
+          <t>7天登录奖励</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>8日ログイン報酬</t>
+          <t>8天登录奖励</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>9日ログイン報酬</t>
+          <t>9天登录奖励</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>連続ログイン1日目</t>
+          <t>连续登录第1天</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>連続ログイン2日目</t>
+          <t>连续登录第2天</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>連続ログイン3日目</t>
+          <t>连续登录第3天</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>連続ログイン4日目</t>
+          <t>连续登录第4天</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>連続ログイン5日目</t>
+          <t>连续登录第5天</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>連続ログイン6日目</t>
+          <t>连续登录第六天</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>連続ログイン7日目</t>
+          <t>连续登录第7天</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>目標日数1日目</t>
+          <t>目标天数第1天</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>目標日数2日目</t>
+          <t>目标天数第2天</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>目標日数3日目</t>
+          <t>目标天数第三天</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>目標日数4日目</t>
+          <t>目标天数第4天</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>目標日数5日目</t>
+          <t>目标天数第五天</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>目標日数6日目</t>
+          <t>目标天数第6天</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>目標日数7日目</t>
+          <t>目标天数第七天</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>目標日数8日目</t>
+          <t>目标天数第8天</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>目標日数9日目</t>
+          <t>目标天数第9天</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>目標日数10日目</t>
+          <t>目标天数第10天</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>目標日数1日目</t>
+          <t>目标天数第1天</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>目標日数2日目</t>
+          <t>目标天数第2天</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>目標日数3日目</t>
+          <t>目标天数第三天</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>目標日数4日目</t>
+          <t>目标天数第4天</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>目標日数5日目</t>
+          <t>目标天数第五天</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>目標日数6日目</t>
+          <t>目标天数第6天</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>目標日数7日目</t>
+          <t>目标天数第七天</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>目標日数8日目</t>
+          <t>目标天数第8天</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>目標日数9日目</t>
+          <t>目标天数第9天</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>目標日数10日目</t>
+          <t>目标天数第10天</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>目標日数11日目</t>
+          <t>目标天数第11天</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>目標日数12日目</t>
+          <t>目标天数第12天</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>目標日数13日目</t>
+          <t>目标天数13天</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>目標日数14日目</t>
+          <t>目标天数第14天</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>目標日数15日目</t>
+          <t>目标天数第15天</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>目標日数16日目</t>
+          <t>目标天数第16天</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>目標日数1日目</t>
+          <t>目标天数第1天</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>目標日数2日目</t>
+          <t>目标天数第2天</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>目標日数3日目</t>
+          <t>目标天数第三天</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>目標日数4日目</t>
+          <t>目标天数第4天</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>目標日数5日目</t>
+          <t>目标天数第五天</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>目標日数6日目</t>
+          <t>目标天数第6天</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>目標日数7日目</t>
+          <t>目标天数第七天</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>目標日数8日目</t>
+          <t>目标天数第8天</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>目標日数9日目</t>
+          <t>目标天数第9天</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>目標日数10日目</t>
+          <t>目标天数第10天</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>目標日数11日目</t>
+          <t>目标天数第11天</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>目標日数12日目</t>
+          <t>目标天数第12天</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>目標日数13日目</t>
+          <t>目标天数13天</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>目標日数14日目</t>
+          <t>目标天数第14天</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>目標日数15日目</t>
+          <t>目标天数第15天</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>目標日数16日目</t>
+          <t>目标天数第16天</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>目標日数1日目</t>
+          <t>目标天数第1天</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>目標日数2日目</t>
+          <t>目标天数第2天</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>目標日数3日目</t>
+          <t>目标天数第三天</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>目標日数4日目</t>
+          <t>目标天数第4天</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>目標日数5日目</t>
+          <t>目标天数第五天</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>目標日数6日目</t>
+          <t>目标天数第6天</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>目標日数7日目</t>
+          <t>目标天数第七天</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>目標日数8日目</t>
+          <t>目标天数第8天</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>目標日数9日目</t>
+          <t>目标天数第9天</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>目標日数10日目</t>
+          <t>目标天数第10天</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>目標日数11日目</t>
+          <t>目标天数第11天</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>目標日数13日目</t>
+          <t>目标天数13天</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>目標日数13日目</t>
+          <t>目标天数13天</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>目標日数14日目</t>
+          <t>目标天数第14天</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>目標日数15日目</t>
+          <t>目标天数第15天</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>目標日数16日目</t>
+          <t>目标天数第16天</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン8日</t>
+          <t>累计登录8天</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン9日</t>
+          <t>累计登录9天</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="D145" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン8日</t>
+          <t>累计登录8天</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン9日</t>
+          <t>累计登录9天</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>周年ログインギフトを1回受け取る</t>
+          <t>获得一份周年登录礼物</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="D155" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="D159" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="D165" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="D167" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン1日</t>
+          <t>累计登录1天</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン2日</t>
+          <t>累计登录2天</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="D173" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン3日</t>
+          <t>累计登录3天</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -8355,7 +8355,7 @@
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン4日</t>
+          <t>累计登录4天</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="D175" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン6日</t>
+          <t>累计登录6天</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="D177" s="3" t="inlineStr">
         <is>
-          <t>累計ログイン7日</t>
+          <t>累计登录7天</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
